--- a/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-structured-info-integer.xlsx
+++ b/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-structured-info-integer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:17:39+00:00</t>
+    <t>2026-08-31T14:07:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
